--- a/plot_map_specialties.xlsx
+++ b/plot_map_specialties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms0952_ox_ac_uk/Documents/OMOP_Validation study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{5748A928-16EB-4036-9481-7DCBACB4E74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50EBB7B0-CB22-4E85-8210-5E6DC65340A3}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{5748A928-16EB-4036-9481-7DCBACB4E74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E24BFEA5-5240-4B51-B075-D5BCCC83FB0E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{434EC9B3-4EB4-4683-B0C6-A3C35AC73F06}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{434EC9B3-4EB4-4683-B0C6-A3C35AC73F06}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1043,18 +1043,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85F18DB-D1DA-4C20-9CDB-58BF1B15F015}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G157"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="45.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" style="8" customWidth="1"/>
     <col min="4" max="4" width="60" style="6" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>186</v>
       </c>
@@ -1074,7 +1075,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -1094,11 +1095,11 @@
         <v>0</v>
       </c>
       <c r="G2" s="5">
-        <f>B2-E2</f>
+        <f t="shared" ref="G2:G33" si="0">B2-E2</f>
         <v>-40.298211915969269</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -1118,11 +1119,11 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <f>B3-E3</f>
+        <f t="shared" si="0"/>
         <v>-40.168211915969273</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -1142,11 +1143,11 @@
         <v>0</v>
       </c>
       <c r="G4" s="5">
-        <f>B4-E4</f>
+        <f t="shared" si="0"/>
         <v>-40.139747357723053</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -1166,11 +1167,11 @@
         <v>0</v>
       </c>
       <c r="G5" s="5">
-        <f>B5-E5</f>
+        <f t="shared" si="0"/>
         <v>-40.139747357723053</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -1190,11 +1191,11 @@
         <v>0</v>
       </c>
       <c r="G6" s="5">
-        <f>B6-E6</f>
+        <f t="shared" si="0"/>
         <v>-39.978211915969268</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -1214,11 +1215,11 @@
         <v>0</v>
       </c>
       <c r="G7" s="5">
-        <f>B7-E7</f>
+        <f t="shared" si="0"/>
         <v>-39.978211915969268</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -1238,11 +1239,11 @@
         <v>0</v>
       </c>
       <c r="G8" s="5">
-        <f>B8-E8</f>
+        <f t="shared" si="0"/>
         <v>-39.978211915969268</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>59</v>
       </c>
@@ -1262,11 +1263,11 @@
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <f>B9-E9</f>
+        <f t="shared" si="0"/>
         <v>-39.978211915969268</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>141</v>
       </c>
@@ -1286,11 +1287,11 @@
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <f>B10-E10</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>120</v>
       </c>
@@ -1310,11 +1311,11 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <f>B11-E11</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -1334,11 +1335,11 @@
         <v>0</v>
       </c>
       <c r="G12" s="5">
-        <f>B12-E12</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -1358,11 +1359,11 @@
         <v>0</v>
       </c>
       <c r="G13" s="5">
-        <f>B13-E13</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -1382,11 +1383,11 @@
         <v>0</v>
       </c>
       <c r="G14" s="5">
-        <f>B14-E14</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -1406,11 +1407,11 @@
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <f>B15-E15</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -1430,11 +1431,11 @@
         <v>0</v>
       </c>
       <c r="G16" s="5">
-        <f>B16-E16</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>145</v>
       </c>
@@ -1454,11 +1455,11 @@
         <v>0</v>
       </c>
       <c r="G17" s="5">
-        <f>B17-E17</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -1478,11 +1479,11 @@
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <f>B18-E18</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -1502,11 +1503,11 @@
         <v>0</v>
       </c>
       <c r="G19" s="5">
-        <f>B19-E19</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -1526,11 +1527,11 @@
         <v>0</v>
       </c>
       <c r="G20" s="5">
-        <f>B20-E20</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -1550,11 +1551,11 @@
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <f>B21-E21</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -1574,11 +1575,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="5">
-        <f>B22-E22</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1598,11 +1599,11 @@
         <v>0</v>
       </c>
       <c r="G23" s="5">
-        <f>B23-E23</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>89</v>
       </c>
@@ -1622,11 +1623,11 @@
         <v>0</v>
       </c>
       <c r="G24" s="5">
-        <f>B24-E24</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>150</v>
       </c>
@@ -1646,11 +1647,11 @@
         <v>0</v>
       </c>
       <c r="G25" s="5">
-        <f>B25-E25</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>139</v>
       </c>
@@ -1670,11 +1671,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="5">
-        <f>B26-E26</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>140</v>
       </c>
@@ -1694,11 +1695,11 @@
         <v>0</v>
       </c>
       <c r="G27" s="5">
-        <f>B27-E27</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>93</v>
       </c>
@@ -1718,11 +1719,11 @@
         <v>0</v>
       </c>
       <c r="G28" s="5">
-        <f>B28-E28</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>115</v>
       </c>
@@ -1742,11 +1743,11 @@
         <v>0</v>
       </c>
       <c r="G29" s="5">
-        <f>B29-E29</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>125</v>
       </c>
@@ -1766,11 +1767,11 @@
         <v>0</v>
       </c>
       <c r="G30" s="5">
-        <f>B30-E30</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -1790,11 +1791,11 @@
         <v>0</v>
       </c>
       <c r="G31" s="5">
-        <f>B31-E31</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>142</v>
       </c>
@@ -1814,11 +1815,11 @@
         <v>0</v>
       </c>
       <c r="G32" s="5">
-        <f>B32-E32</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -1838,11 +1839,11 @@
         <v>0</v>
       </c>
       <c r="G33" s="5">
-        <f>B33-E33</f>
+        <f t="shared" si="0"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>147</v>
       </c>
@@ -1862,11 +1863,11 @@
         <v>0</v>
       </c>
       <c r="G34" s="5">
-        <f>B34-E34</f>
+        <f t="shared" ref="G34:G65" si="1">B34-E34</f>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>138</v>
       </c>
@@ -1886,11 +1887,11 @@
         <v>0</v>
       </c>
       <c r="G35" s="5">
-        <f>B35-E35</f>
+        <f t="shared" si="1"/>
         <v>-39.975484643241998</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>57</v>
       </c>
@@ -1910,11 +1911,11 @@
         <v>0</v>
       </c>
       <c r="G36" s="5">
-        <f>B36-E36</f>
+        <f t="shared" si="1"/>
         <v>-39.00794902505136</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -1934,11 +1935,11 @@
         <v>0</v>
       </c>
       <c r="G37" s="5">
-        <f>B37-E37</f>
+        <f t="shared" si="1"/>
         <v>-35.581545249302607</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>49</v>
       </c>
@@ -1958,11 +1959,11 @@
         <v>0</v>
       </c>
       <c r="G38" s="5">
-        <f>B38-E38</f>
+        <f t="shared" si="1"/>
         <v>-21.363636363636363</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1982,11 +1983,11 @@
         <v>1</v>
       </c>
       <c r="G39" s="5">
-        <f>B39-E39</f>
+        <f t="shared" si="1"/>
         <v>-16.863636363636363</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>180</v>
       </c>
@@ -2006,11 +2007,11 @@
         <v>1</v>
       </c>
       <c r="G40" s="5">
-        <f>B40-E40</f>
+        <f t="shared" si="1"/>
         <v>-13.346666666666668</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>163</v>
       </c>
@@ -2030,11 +2031,11 @@
         <v>1</v>
       </c>
       <c r="G41" s="5">
-        <f>B41-E41</f>
+        <f t="shared" si="1"/>
         <v>-9.0513762074897457</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>164</v>
       </c>
@@ -2054,11 +2055,11 @@
         <v>1</v>
       </c>
       <c r="G42" s="5">
-        <f>B42-E42</f>
+        <f t="shared" si="1"/>
         <v>-9.0513762074897457</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>166</v>
       </c>
@@ -2078,11 +2079,11 @@
         <v>1</v>
       </c>
       <c r="G43" s="5">
-        <f>B43-E43</f>
+        <f t="shared" si="1"/>
         <v>-8.8943915133871485</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>170</v>
       </c>
@@ -2102,11 +2103,11 @@
         <v>1</v>
       </c>
       <c r="G44" s="5">
-        <f>B44-E44</f>
+        <f t="shared" si="1"/>
         <v>-4.6666666666666643</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>77</v>
       </c>
@@ -2126,11 +2127,11 @@
         <v>0</v>
       </c>
       <c r="G45" s="5">
-        <f>B45-E45</f>
+        <f t="shared" si="1"/>
         <v>-4.2482119159692715</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -2150,11 +2151,11 @@
         <v>0</v>
       </c>
       <c r="G46" s="5">
-        <f>B46-E46</f>
+        <f t="shared" si="1"/>
         <v>-4.2482119159692715</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2174,11 +2175,11 @@
         <v>0</v>
       </c>
       <c r="G47" s="5">
-        <f>B47-E47</f>
+        <f t="shared" si="1"/>
         <v>-4.2482119159692715</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>109</v>
       </c>
@@ -2198,11 +2199,11 @@
         <v>0</v>
       </c>
       <c r="G48" s="5">
-        <f>B48-E48</f>
+        <f t="shared" si="1"/>
         <v>-4.2482119159692715</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -2222,11 +2223,11 @@
         <v>0</v>
       </c>
       <c r="G49" s="5">
-        <f>B49-E49</f>
+        <f t="shared" si="1"/>
         <v>-4.2482119159692715</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>92</v>
       </c>
@@ -2246,11 +2247,11 @@
         <v>0</v>
       </c>
       <c r="G50" s="5">
-        <f>B50-E50</f>
+        <f t="shared" si="1"/>
         <v>-4.2482119159692715</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -2270,11 +2271,11 @@
         <v>0</v>
       </c>
       <c r="G51" s="5">
-        <f>B51-E51</f>
+        <f t="shared" si="1"/>
         <v>-4.2482119159692715</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>71</v>
       </c>
@@ -2294,11 +2295,11 @@
         <v>0</v>
       </c>
       <c r="G52" s="5">
-        <f>B52-E52</f>
+        <f t="shared" si="1"/>
         <v>-4.2482119159692715</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>123</v>
       </c>
@@ -2318,11 +2319,11 @@
         <v>0</v>
       </c>
       <c r="G53" s="5">
-        <f>B53-E53</f>
+        <f t="shared" si="1"/>
         <v>-4.2482119159692715</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>160</v>
       </c>
@@ -2342,11 +2343,11 @@
         <v>1</v>
       </c>
       <c r="G54" s="5">
-        <f>B54-E54</f>
+        <f t="shared" si="1"/>
         <v>-2.7742600679281901</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>158</v>
       </c>
@@ -2366,11 +2367,11 @@
         <v>1</v>
       </c>
       <c r="G55" s="5">
-        <f>B55-E55</f>
+        <f t="shared" si="1"/>
         <v>-2.75</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>129</v>
       </c>
@@ -2390,11 +2391,11 @@
         <v>0</v>
       </c>
       <c r="G56" s="5">
-        <f>B56-E56</f>
+        <f t="shared" si="1"/>
         <v>-2.2482119159692715</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -2414,11 +2415,11 @@
         <v>0</v>
       </c>
       <c r="G57" s="5">
-        <f>B57-E57</f>
+        <f t="shared" si="1"/>
         <v>-2.2482119159692715</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -2438,11 +2439,11 @@
         <v>0</v>
       </c>
       <c r="G58" s="5">
-        <f>B58-E58</f>
+        <f t="shared" si="1"/>
         <v>-2.2482119159692715</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>84</v>
       </c>
@@ -2462,11 +2463,11 @@
         <v>0</v>
       </c>
       <c r="G59" s="5">
-        <f>B59-E59</f>
+        <f t="shared" si="1"/>
         <v>-2.2482119159692715</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>167</v>
       </c>
@@ -2486,11 +2487,11 @@
         <v>1</v>
       </c>
       <c r="G60" s="5">
-        <f>B60-E60</f>
+        <f t="shared" si="1"/>
         <v>-0.6666666666666643</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>157</v>
       </c>
@@ -2510,11 +2511,11 @@
         <v>0</v>
       </c>
       <c r="G61" s="5">
-        <f>B61-E61</f>
+        <f t="shared" si="1"/>
         <v>-0.64494104068339886</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>156</v>
       </c>
@@ -2534,11 +2535,11 @@
         <v>0</v>
       </c>
       <c r="G62" s="5">
-        <f>B62-E62</f>
+        <f t="shared" si="1"/>
         <v>-0.64494104068339886</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>151</v>
       </c>
@@ -2558,11 +2559,11 @@
         <v>0</v>
       </c>
       <c r="G63" s="5">
-        <f>B63-E63</f>
+        <f t="shared" si="1"/>
         <v>-0.64494104068339886</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>154</v>
       </c>
@@ -2582,11 +2583,11 @@
         <v>0</v>
       </c>
       <c r="G64" s="5">
-        <f>B64-E64</f>
+        <f t="shared" si="1"/>
         <v>-0.64494104068339886</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>40</v>
       </c>
@@ -2606,11 +2607,11 @@
         <v>0</v>
       </c>
       <c r="G65" s="5">
-        <f>B65-E65</f>
+        <f t="shared" si="1"/>
         <v>-0.5993118962551276</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>184</v>
       </c>
@@ -2630,11 +2631,11 @@
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <f>B66-E66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" ref="G66:G97" si="2">B66-E66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>21</v>
       </c>
@@ -2654,11 +2655,11 @@
         <v>0</v>
       </c>
       <c r="G67" s="5">
-        <f>B67-E67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>174</v>
       </c>
@@ -2678,11 +2679,11 @@
         <v>0</v>
       </c>
       <c r="G68" s="5">
-        <f>B68-E68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>179</v>
       </c>
@@ -2702,11 +2703,11 @@
         <v>0</v>
       </c>
       <c r="G69" s="5">
-        <f>B69-E69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>178</v>
       </c>
@@ -2726,11 +2727,11 @@
         <v>0</v>
       </c>
       <c r="G70" s="5">
-        <f>B70-E70</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>177</v>
       </c>
@@ -2750,11 +2751,11 @@
         <v>0</v>
       </c>
       <c r="G71" s="5">
-        <f>B71-E71</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>176</v>
       </c>
@@ -2774,11 +2775,11 @@
         <v>0</v>
       </c>
       <c r="G72" s="5">
-        <f>B72-E72</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>36</v>
       </c>
@@ -2798,11 +2799,11 @@
         <v>0</v>
       </c>
       <c r="G73" s="5">
-        <f>B73-E73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>0</v>
       </c>
@@ -2822,11 +2823,11 @@
         <v>1</v>
       </c>
       <c r="G74" s="5">
-        <f>B74-E74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>2</v>
       </c>
@@ -2846,11 +2847,11 @@
         <v>1</v>
       </c>
       <c r="G75" s="5">
-        <f>B75-E75</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>4</v>
       </c>
@@ -2870,11 +2871,11 @@
         <v>1</v>
       </c>
       <c r="G76" s="5">
-        <f>B76-E76</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2894,11 +2895,11 @@
         <v>1</v>
       </c>
       <c r="G77" s="5">
-        <f>B77-E77</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>46</v>
       </c>
@@ -2918,11 +2919,11 @@
         <v>1</v>
       </c>
       <c r="G78" s="5">
-        <f>B78-E78</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>48</v>
       </c>
@@ -2942,11 +2943,11 @@
         <v>1</v>
       </c>
       <c r="G79" s="5">
-        <f>B79-E79</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>8</v>
       </c>
@@ -2966,11 +2967,11 @@
         <v>1</v>
       </c>
       <c r="G80" s="5">
-        <f>B80-E80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>10</v>
       </c>
@@ -2990,11 +2991,11 @@
         <v>1</v>
       </c>
       <c r="G81" s="5">
-        <f>B81-E81</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -3014,11 +3015,11 @@
         <v>1</v>
       </c>
       <c r="G82" s="5">
-        <f>B82-E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -3038,11 +3039,11 @@
         <v>1</v>
       </c>
       <c r="G83" s="5">
-        <f>B83-E83</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -3062,11 +3063,11 @@
         <v>1</v>
       </c>
       <c r="G84" s="5">
-        <f>B84-E84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -3086,11 +3087,11 @@
         <v>1</v>
       </c>
       <c r="G85" s="5">
-        <f>B85-E85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -3110,11 +3111,11 @@
         <v>1</v>
       </c>
       <c r="G86" s="5">
-        <f>B86-E86</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>19</v>
       </c>
@@ -3134,11 +3135,11 @@
         <v>1</v>
       </c>
       <c r="G87" s="5">
-        <f>B87-E87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>23</v>
       </c>
@@ -3158,11 +3159,11 @@
         <v>1</v>
       </c>
       <c r="G88" s="5">
-        <f>B88-E88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -3182,11 +3183,11 @@
         <v>1</v>
       </c>
       <c r="G89" s="5">
-        <f>B89-E89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>27</v>
       </c>
@@ -3206,11 +3207,11 @@
         <v>1</v>
       </c>
       <c r="G90" s="5">
-        <f>B90-E90</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>29</v>
       </c>
@@ -3230,11 +3231,11 @@
         <v>1</v>
       </c>
       <c r="G91" s="5">
-        <f>B91-E91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>31</v>
       </c>
@@ -3254,11 +3255,11 @@
         <v>1</v>
       </c>
       <c r="G92" s="5">
-        <f>B92-E92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>173</v>
       </c>
@@ -3278,11 +3279,11 @@
         <v>1</v>
       </c>
       <c r="G93" s="5">
-        <f>B93-E93</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>171</v>
       </c>
@@ -3302,11 +3303,11 @@
         <v>1</v>
       </c>
       <c r="G94" s="5">
-        <f>B94-E94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>33</v>
       </c>
@@ -3326,11 +3327,11 @@
         <v>1</v>
       </c>
       <c r="G95" s="5">
-        <f>B95-E95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>35</v>
       </c>
@@ -3350,11 +3351,11 @@
         <v>1</v>
       </c>
       <c r="G96" s="5">
-        <f>B96-E96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>38</v>
       </c>
@@ -3374,11 +3375,11 @@
         <v>1</v>
       </c>
       <c r="G97" s="5">
-        <f>B97-E97</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>42</v>
       </c>
@@ -3398,11 +3399,11 @@
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <f>B98-E98</f>
+        <f t="shared" ref="G98:G129" si="3">B98-E98</f>
         <v>0.5993118962551276</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>155</v>
       </c>
@@ -3422,11 +3423,11 @@
         <v>0</v>
       </c>
       <c r="G99" s="5">
-        <f>B99-E99</f>
+        <f t="shared" si="3"/>
         <v>0.66566501992266169</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>90</v>
       </c>
@@ -3446,11 +3447,11 @@
         <v>0</v>
       </c>
       <c r="G100" s="5">
-        <f>B100-E100</f>
+        <f t="shared" si="3"/>
         <v>1.7517880840307285</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>153</v>
       </c>
@@ -3470,11 +3471,11 @@
         <v>0</v>
       </c>
       <c r="G101" s="5">
-        <f>B101-E101</f>
+        <f t="shared" si="3"/>
         <v>1.9140991428109329</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>159</v>
       </c>
@@ -3494,11 +3495,11 @@
         <v>1</v>
       </c>
       <c r="G102" s="5">
-        <f>B102-E102</f>
+        <f t="shared" si="3"/>
         <v>2.75</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>137</v>
       </c>
@@ -3518,11 +3519,11 @@
         <v>0</v>
       </c>
       <c r="G103" s="5">
-        <f>B103-E103</f>
+        <f t="shared" si="3"/>
         <v>2.7517880840307285</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>114</v>
       </c>
@@ -3542,11 +3543,11 @@
         <v>0</v>
       </c>
       <c r="G104" s="5">
-        <f>B104-E104</f>
+        <f t="shared" si="3"/>
         <v>2.7517880840307285</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>100</v>
       </c>
@@ -3566,11 +3567,11 @@
         <v>0</v>
       </c>
       <c r="G105" s="5">
-        <f>B105-E105</f>
+        <f t="shared" si="3"/>
         <v>2.7517880840307285</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>117</v>
       </c>
@@ -3590,11 +3591,11 @@
         <v>0</v>
       </c>
       <c r="G106" s="5">
-        <f>B106-E106</f>
+        <f t="shared" si="3"/>
         <v>2.7517880840307285</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>113</v>
       </c>
@@ -3614,11 +3615,11 @@
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <f>B107-E107</f>
+        <f t="shared" si="3"/>
         <v>2.7517880840307285</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>79</v>
       </c>
@@ -3638,11 +3639,11 @@
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <f>B108-E108</f>
+        <f t="shared" si="3"/>
         <v>2.7517880840307285</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>135</v>
       </c>
@@ -3662,11 +3663,11 @@
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <f>B109-E109</f>
+        <f t="shared" si="3"/>
         <v>2.7517880840307285</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>85</v>
       </c>
@@ -3686,11 +3687,11 @@
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <f>B110-E110</f>
+        <f t="shared" si="3"/>
         <v>2.7517880840307285</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>162</v>
       </c>
@@ -3710,11 +3711,11 @@
         <v>1</v>
       </c>
       <c r="G111" s="5">
-        <f>B111-E111</f>
+        <f t="shared" si="3"/>
         <v>2.7742600679281901</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>56</v>
       </c>
@@ -3734,11 +3735,11 @@
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <f>B112-E112</f>
+        <f t="shared" si="3"/>
         <v>3.0017880840307285</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>54</v>
       </c>
@@ -3758,11 +3759,11 @@
         <v>0</v>
       </c>
       <c r="G113" s="5">
-        <f>B113-E113</f>
+        <f t="shared" si="3"/>
         <v>3.0017880840307285</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>55</v>
       </c>
@@ -3782,11 +3783,11 @@
         <v>0</v>
       </c>
       <c r="G114" s="5">
-        <f>B114-E114</f>
+        <f t="shared" si="3"/>
         <v>3.0017880840307285</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>52</v>
       </c>
@@ -3806,11 +3807,11 @@
         <v>0</v>
       </c>
       <c r="G115" s="5">
-        <f>B115-E115</f>
+        <f t="shared" si="3"/>
         <v>3.0017880840307285</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>146</v>
       </c>
@@ -3830,11 +3831,11 @@
         <v>0</v>
       </c>
       <c r="G116" s="5">
-        <f>B116-E116</f>
+        <f t="shared" si="3"/>
         <v>3.7517880840307285</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>169</v>
       </c>
@@ -3854,11 +3855,11 @@
         <v>1</v>
       </c>
       <c r="G117" s="5">
-        <f>B117-E117</f>
+        <f t="shared" si="3"/>
         <v>5.3333333333333357</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>182</v>
       </c>
@@ -3878,11 +3879,11 @@
         <v>1</v>
       </c>
       <c r="G118" s="5">
-        <f>B118-E118</f>
+        <f t="shared" si="3"/>
         <v>6.673333333333332</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>183</v>
       </c>
@@ -3902,11 +3903,11 @@
         <v>1</v>
       </c>
       <c r="G119" s="5">
-        <f>B119-E119</f>
+        <f t="shared" si="3"/>
         <v>6.673333333333332</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>83</v>
       </c>
@@ -3926,11 +3927,11 @@
         <v>0</v>
       </c>
       <c r="G120" s="5">
-        <f>B120-E120</f>
+        <f t="shared" si="3"/>
         <v>6.7517880840307285</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>118</v>
       </c>
@@ -3950,11 +3951,11 @@
         <v>0</v>
       </c>
       <c r="G121" s="5">
-        <f>B121-E121</f>
+        <f t="shared" si="3"/>
         <v>6.7517880840307285</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>136</v>
       </c>
@@ -3974,11 +3975,11 @@
         <v>0</v>
       </c>
       <c r="G122" s="5">
-        <f>B122-E122</f>
+        <f t="shared" si="3"/>
         <v>6.7517880840307285</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>97</v>
       </c>
@@ -3998,11 +3999,11 @@
         <v>0</v>
       </c>
       <c r="G123" s="5">
-        <f>B123-E123</f>
+        <f t="shared" si="3"/>
         <v>15.751788084030728</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>102</v>
       </c>
@@ -4022,11 +4023,11 @@
         <v>0</v>
       </c>
       <c r="G124" s="5">
-        <f>B124-E124</f>
+        <f t="shared" si="3"/>
         <v>15.751788084030728</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>96</v>
       </c>
@@ -4046,11 +4047,11 @@
         <v>0</v>
       </c>
       <c r="G125" s="5">
-        <f>B125-E125</f>
+        <f t="shared" si="3"/>
         <v>15.751788084030728</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>112</v>
       </c>
@@ -4070,11 +4071,11 @@
         <v>0</v>
       </c>
       <c r="G126" s="5">
-        <f>B126-E126</f>
+        <f t="shared" si="3"/>
         <v>15.751788084030728</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>131</v>
       </c>
@@ -4094,11 +4095,11 @@
         <v>0</v>
       </c>
       <c r="G127" s="5">
-        <f>B127-E127</f>
+        <f t="shared" si="3"/>
         <v>15.751788084030728</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>116</v>
       </c>
@@ -4118,11 +4119,11 @@
         <v>0</v>
       </c>
       <c r="G128" s="5">
-        <f>B128-E128</f>
+        <f t="shared" si="3"/>
         <v>15.751788084030728</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>124</v>
       </c>
@@ -4142,11 +4143,11 @@
         <v>0</v>
       </c>
       <c r="G129" s="5">
-        <f>B129-E129</f>
+        <f t="shared" si="3"/>
         <v>15.751788084030728</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>45</v>
       </c>
@@ -4166,11 +4167,11 @@
         <v>1</v>
       </c>
       <c r="G130" s="5">
-        <f>B130-E130</f>
+        <f t="shared" ref="G130:G157" si="4">B130-E130</f>
         <v>16.863636363636363</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>51</v>
       </c>
@@ -4190,11 +4191,11 @@
         <v>0</v>
       </c>
       <c r="G131" s="5">
-        <f>B131-E131</f>
+        <f t="shared" si="4"/>
         <v>21.363636363636363</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>101</v>
       </c>
@@ -4214,11 +4215,11 @@
         <v>0</v>
       </c>
       <c r="G132" s="5">
-        <f>B132-E132</f>
+        <f t="shared" si="4"/>
         <v>26.751788084030728</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>78</v>
       </c>
@@ -4238,11 +4239,11 @@
         <v>0</v>
       </c>
       <c r="G133" s="5">
-        <f>B133-E133</f>
+        <f t="shared" si="4"/>
         <v>26.751788084030728</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>132</v>
       </c>
@@ -4262,11 +4263,11 @@
         <v>0</v>
       </c>
       <c r="G134" s="5">
-        <f>B134-E134</f>
+        <f t="shared" si="4"/>
         <v>26.751788084030728</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>122</v>
       </c>
@@ -4286,11 +4287,11 @@
         <v>0</v>
       </c>
       <c r="G135" s="5">
-        <f>B135-E135</f>
+        <f t="shared" si="4"/>
         <v>26.751788084030728</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>94</v>
       </c>
@@ -4310,11 +4311,11 @@
         <v>0</v>
       </c>
       <c r="G136" s="5">
-        <f>B136-E136</f>
+        <f t="shared" si="4"/>
         <v>26.751788084030728</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>103</v>
       </c>
@@ -4334,11 +4335,11 @@
         <v>0</v>
       </c>
       <c r="G137" s="5">
-        <f>B137-E137</f>
+        <f t="shared" si="4"/>
         <v>26.751788084030728</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>121</v>
       </c>
@@ -4358,11 +4359,11 @@
         <v>0</v>
       </c>
       <c r="G138" s="5">
-        <f>B138-E138</f>
+        <f t="shared" si="4"/>
         <v>26.751788084030728</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>165</v>
       </c>
@@ -4382,11 +4383,11 @@
         <v>1</v>
       </c>
       <c r="G139" s="5">
-        <f>B139-E139</f>
+        <f t="shared" si="4"/>
         <v>26.997143928366633</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>127</v>
       </c>
@@ -4406,11 +4407,11 @@
         <v>0</v>
       </c>
       <c r="G140" s="5">
-        <f>B140-E140</f>
+        <f t="shared" si="4"/>
         <v>27.751788084030728</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>95</v>
       </c>
@@ -4430,11 +4431,11 @@
         <v>0</v>
       </c>
       <c r="G141" s="5">
-        <f>B141-E141</f>
+        <f t="shared" si="4"/>
         <v>35.751788084030728</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>134</v>
       </c>
@@ -4454,11 +4455,11 @@
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <f>B142-E142</f>
+        <f t="shared" si="4"/>
         <v>41.751788084030728</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>133</v>
       </c>
@@ -4478,11 +4479,11 @@
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <f>B143-E143</f>
+        <f t="shared" si="4"/>
         <v>41.751788084030728</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>144</v>
       </c>
@@ -4502,11 +4503,11 @@
         <v>0</v>
       </c>
       <c r="G144" s="5">
-        <f>B144-E144</f>
+        <f t="shared" si="4"/>
         <v>41.751788084030728</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>149</v>
       </c>
@@ -4526,11 +4527,11 @@
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <f>B145-E145</f>
+        <f t="shared" si="4"/>
         <v>41.751788084030728</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>110</v>
       </c>
@@ -4550,11 +4551,11 @@
         <v>0</v>
       </c>
       <c r="G146" s="5">
-        <f>B146-E146</f>
+        <f t="shared" si="4"/>
         <v>41.751788084030728</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>105</v>
       </c>
@@ -4574,11 +4575,11 @@
         <v>0</v>
       </c>
       <c r="G147" s="5">
-        <f>B147-E147</f>
+        <f t="shared" si="4"/>
         <v>41.751788084030728</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>81</v>
       </c>
@@ -4598,11 +4599,11 @@
         <v>0</v>
       </c>
       <c r="G148" s="5">
-        <f>B148-E148</f>
+        <f t="shared" si="4"/>
         <v>74.251788084030721</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>76</v>
       </c>
@@ -4622,11 +4623,11 @@
         <v>0</v>
       </c>
       <c r="G149" s="5">
-        <f>B149-E149</f>
+        <f t="shared" si="4"/>
         <v>74.251788084030721</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>104</v>
       </c>
@@ -4646,11 +4647,11 @@
         <v>0</v>
       </c>
       <c r="G150" s="5">
-        <f>B150-E150</f>
+        <f t="shared" si="4"/>
         <v>74.251788084030721</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>111</v>
       </c>
@@ -4670,11 +4671,11 @@
         <v>0</v>
       </c>
       <c r="G151" s="5">
-        <f>B151-E151</f>
+        <f t="shared" si="4"/>
         <v>74.251788084030721</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>107</v>
       </c>
@@ -4694,11 +4695,11 @@
         <v>0</v>
       </c>
       <c r="G152" s="5">
-        <f>B152-E152</f>
+        <f t="shared" si="4"/>
         <v>74.251788084030721</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>126</v>
       </c>
@@ -4718,11 +4719,11 @@
         <v>0</v>
       </c>
       <c r="G153" s="5">
-        <f>B153-E153</f>
+        <f t="shared" si="4"/>
         <v>74.251788084030721</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>80</v>
       </c>
@@ -4742,11 +4743,11 @@
         <v>0</v>
       </c>
       <c r="G154" s="5">
-        <f>B154-E154</f>
+        <f t="shared" si="4"/>
         <v>74.251788084030721</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>130</v>
       </c>
@@ -4766,11 +4767,11 @@
         <v>0</v>
       </c>
       <c r="G155" s="5">
-        <f>B155-E155</f>
+        <f t="shared" si="4"/>
         <v>74.251788084030721</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>119</v>
       </c>
@@ -4790,11 +4791,11 @@
         <v>0</v>
       </c>
       <c r="G156" s="5">
-        <f>B156-E156</f>
+        <f t="shared" si="4"/>
         <v>107.75178808403072</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>148</v>
       </c>
@@ -4814,12 +4815,17 @@
         <v>0</v>
       </c>
       <c r="G157" s="5">
-        <f>B157-E157</f>
+        <f t="shared" si="4"/>
         <v>108.75178808403072</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G157" xr:uid="{A85F18DB-D1DA-4C20-9CDB-58BF1B15F015}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="GP Registrar"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G157">
       <sortCondition ref="G1:G157"/>
     </sortState>
